--- a/analysis/somerton_2002/data/best_models.xlsx
+++ b/analysis/somerton_2002/data/best_models.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\sratio\analysis\somerton_2002\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35B81B0-DCB8-4F47-BDE9-BB963FE49578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9928C146-4EF1-45BA-88B8-606810EEDBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27480" yWindow="3900" windowWidth="13155" windowHeight="15345" xr2:uid="{15F83652-5193-4201-9709-5BFFF6625622}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="38700" windowHeight="15345" xr2:uid="{15F83652-5193-4201-9709-5BFFF6625622}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,24 +65,12 @@
     <t>CCR</t>
   </si>
   <si>
-    <t>ccr_beta1</t>
-  </si>
-  <si>
     <t>Tanner crab (male)</t>
   </si>
   <si>
-    <t>ccr_bin1</t>
-  </si>
-  <si>
     <t>red king crab (female)</t>
   </si>
   <si>
-    <t>nb10</t>
-  </si>
-  <si>
-    <t>ccr_bin2</t>
-  </si>
-  <si>
     <t>red king crab (male)</t>
   </si>
   <si>
@@ -95,9 +83,6 @@
     <t>snow crab (male)</t>
   </si>
   <si>
-    <t>bb1</t>
-  </si>
-  <si>
     <t>reason</t>
   </si>
   <si>
@@ -143,24 +128,6 @@
     <t>Lowest RMSE. Some residual pattern.</t>
   </si>
   <si>
-    <t>bb7</t>
-  </si>
-  <si>
-    <t>nb9</t>
-  </si>
-  <si>
-    <t>nb6</t>
-  </si>
-  <si>
-    <t>ccr_beta8</t>
-  </si>
-  <si>
-    <t>ccr_bin3</t>
-  </si>
-  <si>
-    <t>nb11</t>
-  </si>
-  <si>
     <t>Second highest RMSE and better residual pattern than nb5</t>
   </si>
   <si>
@@ -173,25 +140,58 @@
     <t>Lowest RMSE, some residual violations but other models with similar RMSE also have residual patterns</t>
   </si>
   <si>
-    <t>bb5</t>
-  </si>
-  <si>
     <t>Fourth highest RMSE; bin3, bb5, bin2 had residual patterns</t>
   </si>
   <si>
-    <t>ccr_beta5</t>
-  </si>
-  <si>
     <t>Third lowest RMSE. ccr_bin2 and ccr_beta2 had residual patterns</t>
   </si>
   <si>
     <t>Fourth highest RMSE. OLS mean, lognormal1, and lognormal2 had violations</t>
   </si>
   <si>
-    <t>bb6</t>
-  </si>
-  <si>
     <t>Lowest RMSE, residuals OK, maybe minor violation</t>
+  </si>
+  <si>
+    <t>NB9</t>
+  </si>
+  <si>
+    <t>BB1</t>
+  </si>
+  <si>
+    <t>CCR_BB1</t>
+  </si>
+  <si>
+    <t>BB7</t>
+  </si>
+  <si>
+    <t>CCR_BI1</t>
+  </si>
+  <si>
+    <t>NB6</t>
+  </si>
+  <si>
+    <t>BB5</t>
+  </si>
+  <si>
+    <t>CCR_BI2</t>
+  </si>
+  <si>
+    <t>BB6</t>
+  </si>
+  <si>
+    <t>NB11</t>
+  </si>
+  <si>
+    <t>CCR_BB8</t>
+  </si>
+  <si>
+    <t>NB10</t>
+  </si>
+  <si>
+    <t>CCR_BI3</t>
+  </si>
+  <si>
+    <t>CCR_BB5</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -591,10 +591,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -605,10 +605,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -622,7 +622,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -633,29 +633,29 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -664,82 +664,82 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -748,82 +748,82 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -832,54 +832,54 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -888,35 +888,35 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
